--- a/assetcore/public/import_templates/01b_khoa_phong.xlsx
+++ b/assetcore/public/import_templates/01b_khoa_phong.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📋 HƯỚNG DẪN IMPORT: Khoa phòng (Department)  |  Điền dữ liệu từ hàng 5 trở xuống. Cột đỏ = bắt buộc. Không xóa hàng 2-4.</t>
+          <t>📋 HƯỚNG DẪN IMPORT: Khoa phòng (Department)  |  Điền dữ liệu từ HÀNG 6 trở xuống (hàng 5 là ví dụ mẫu, hệ thống bỏ qua). Cột đỏ = bắt buộc. Không xoá/không sửa hàng 1-5. Cột tham chiếu (danh mục, khoa phòng, vị trí, model, nhà cung cấp) điền TÊN, không điền mã.</t>
         </is>
       </c>
     </row>
@@ -644,12 +644,12 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Tên khoa cha (nếu là khoa con). Phải tồn tại trong hệ thống.</t>
+          <t>Tên khoa/phòng cấp trên (nếu là khoa con). Điền TÊN, KHÔNG điền mã hệ thống. Phải tồn tại trong hệ thống hoặc được khai ở hàng phía trên.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Email của trưởng khoa (User phải tồn tại trong hệ thống).</t>
+          <t>Email của trưởng khoa. Tài khoản phải tồn tại; sai email thì dòng vẫn nhập được nhưng để trống ô này.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -1720,10 +1720,10 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="G5:G105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="G6:G105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="H6:H105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>

--- a/assetcore/public/import_templates/01b_khoa_phong.xlsx
+++ b/assetcore/public/import_templates/01b_khoa_phong.xlsx
@@ -1720,10 +1720,10 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="G6:G105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="G6:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="H6:H105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="H6:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>
